--- a/survey_templates/036_seasonal_menu_selection_poll--survey_templates.xlsx
+++ b/survey_templates/036_seasonal_menu_selection_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_poll</t>
+          <t>seasonal_menu_selection_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_date</t>
+          <t>seasonal_menu_selection_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>seasonal menu selection date</t>
+          <t>What is your favorite seasonal menu item?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_time</t>
+          <t>seasonal_menu_selection_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>seasonal menu selection time</t>
+          <t>Which time of year do you prefer?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_note</t>
+          <t>seasonal_menu_selection_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>seasonal menu selection note</t>
+          <t>Do you prefer sweet or savory flavors?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_1</t>
+          <t>seasonal_menu_selection_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>Which cooking method do you prefer?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_2</t>
+          <t>seasonal_menu_selection_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>Do you have any dietary restrictions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_3</t>
+          <t>seasonal_menu_selection_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>What is your favorite ingredient?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_4</t>
+          <t>seasonal_menu_selection_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>Do you prefer meat or vegetarian/vegan options?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_5</t>
+          <t>seasonal_menu_selection_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>Which cuisine do you prefer?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_6</t>
+          <t>seasonal_menu_selection_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>How often do you visit the menu?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_7</t>
+          <t>seasonal_menu_selection_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>What is your budget for the menu?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_8</t>
+          <t>seasonal_menu_selection_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Which item do you prefer?</t>
+          <t>Any additional comments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_9</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_12</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_13</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_16</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Which item do you prefer?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,731 +827,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_1_choices</t>
+          <t>seasonal_menu_selection_page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>item_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>item 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_1_choices</t>
+          <t>seasonal_menu_selection_page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>item_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>item 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_1_choices</t>
+          <t>seasonal_menu_selection_page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'item_3',_'value':_'item_3'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'item 3', 'value': 'item 3'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_2_choices</t>
+          <t>seasonal_menu_selection_page_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_2_choices</t>
+          <t>seasonal_menu_selection_page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_3_choices</t>
+          <t>seasonal_menu_selection_page_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>sweet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Sweet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_3_choices</t>
+          <t>seasonal_menu_selection_page_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>savory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Savory</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_4_choices</t>
+          <t>seasonal_menu_selection_page_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_4_choices</t>
+          <t>seasonal_menu_selection_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>grilled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Grilled</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_5_choices</t>
+          <t>seasonal_menu_selection_page_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>baked</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Baked</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_5_choices</t>
+          <t>seasonal_menu_selection_page_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>fried</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Fried</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_6_choices</t>
+          <t>seasonal_menu_selection_page_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_6_choices</t>
+          <t>seasonal_menu_selection_page_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_7_choices</t>
+          <t>seasonal_menu_selection_page_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>item_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>item 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_7_choices</t>
+          <t>seasonal_menu_selection_page_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>item_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>item 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_8_choices</t>
+          <t>seasonal_menu_selection_page_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_8_choices</t>
+          <t>seasonal_menu_selection_page_8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_9_choices</t>
+          <t>seasonal_menu_selection_page_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_9_choices</t>
+          <t>seasonal_menu_selection_page_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_10_choices</t>
+          <t>seasonal_menu_selection_page_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>mexican</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Mexican</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_10_choices</t>
+          <t>seasonal_menu_selection_page_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_11_choices</t>
+          <t>seasonal_menu_selection_page_10_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_11_choices</t>
+          <t>seasonal_menu_selection_page_10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_12_choices</t>
+          <t>seasonal_menu_selection_page_10_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_12_choices</t>
+          <t>seasonal_menu_selection_page_10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_13_choices</t>
+          <t>seasonal_menu_selection_page_11_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>$10-$20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>$10-$20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_13_choices</t>
+          <t>seasonal_menu_selection_page_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>$20-$30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>$20-$30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_14_choices</t>
+          <t>seasonal_menu_selection_page_11_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
+          <t>$30-$40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
+          <t>$30-$40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>seasonal_menu_selection_14_choices</t>
+          <t>seasonal_menu_selection_page_11_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
+          <t>$40+</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_15_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_15_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_16_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_16_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_17_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_17_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_18_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_18_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_19_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_19_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_20_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_20_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_21_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'item_1',_'value':_'item_1'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'item 1', 'value': 'item 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>seasonal_menu_selection_21_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'label':_'item_2',_'value':_'item_2'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'label': 'item 2', 'value': 'item 2'}</t>
+          <t>$40+</t>
         </is>
       </c>
     </row>
